--- a/HR_Analytics_Dashboard.xlsx
+++ b/HR_Analytics_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\InceptionBD\HR-Data-Analytics-Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B15D2B8-3456-49FB-B4E8-B788229DB872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620470C1-C070-4C16-BA7B-D488B99C6155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -2811,18 +2811,60 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="252">
+  <dxfs count="450">
     <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="1">
-            <color theme="1" tint="0.34900967436750391"/>
-          </stop>
-        </gradientFill>
-      </fill>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -3473,10 +3515,43 @@
       <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -3494,13 +3569,502 @@
       <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3525,6 +4089,24 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -3818,10 +4400,22 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color theme="1" tint="0.34900967436750391"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Slicer Style 1" pivot="0" table="0" count="1" xr9:uid="{0DDA6ECE-B2F6-48A7-9C23-00E3C31B68E1}">
-      <tableStyleElement type="wholeTable" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="449"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3862,7 +4456,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr sz="720" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
                     <a:lumMod val="95000"/>
@@ -3900,7 +4494,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+            <a:defRPr sz="720" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="lt1">
                   <a:lumMod val="95000"/>
@@ -4027,49 +4621,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4081,13 +4633,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="lt1">
                       <a:lumMod val="85000"/>
@@ -4101,7 +4651,7 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="inEnd"/>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -4182,13 +4732,11 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="lt1">
                         <a:lumMod val="85000"/>
@@ -4202,7 +4750,7 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="inEnd"/>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -4295,7 +4843,7 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="inEnd"/>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -4337,7 +4885,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
                     <a:lumMod val="85000"/>
@@ -4395,7 +4943,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
                     <a:lumMod val="85000"/>
@@ -4463,7 +5011,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="600"/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -8608,7 +9156,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr sz="720" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
                     <a:lumMod val="95000"/>
@@ -8646,7 +9194,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+            <a:defRPr sz="720" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="lt1">
                   <a:lumMod val="95000"/>
@@ -8743,49 +9291,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -8797,13 +9303,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="lt1">
                       <a:lumMod val="85000"/>
@@ -8817,7 +9321,7 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="inEnd"/>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -8898,13 +9402,11 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="lt1">
                         <a:lumMod val="85000"/>
@@ -8918,7 +9420,7 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="inEnd"/>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -9029,7 +9531,7 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="inEnd"/>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -9071,7 +9573,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
                     <a:lumMod val="85000"/>
@@ -9129,7 +9631,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
                     <a:lumMod val="85000"/>
@@ -9197,7 +9699,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="600"/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -9249,7 +9751,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr sz="720" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
                     <a:lumMod val="95000"/>
@@ -9287,7 +9789,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+            <a:defRPr sz="720" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="lt1">
                   <a:lumMod val="95000"/>
@@ -9393,8 +9895,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -9406,13 +9907,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="lt1">
                       <a:lumMod val="85000"/>
@@ -9485,21 +9984,21 @@
           <a:gradFill rotWithShape="1">
             <a:gsLst>
               <a:gs pos="0">
-                <a:schemeClr val="accent2">
+                <a:schemeClr val="accent1">
                   <a:satMod val="103000"/>
                   <a:lumMod val="102000"/>
                   <a:tint val="94000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="50000">
-                <a:schemeClr val="accent2">
+                <a:schemeClr val="accent1">
                   <a:satMod val="110000"/>
                   <a:lumMod val="100000"/>
                   <a:shade val="100000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="100000">
-                <a:schemeClr val="accent2">
+                <a:schemeClr val="accent1">
                   <a:lumMod val="99000"/>
                   <a:satMod val="120000"/>
                   <a:shade val="78000"/>
@@ -9526,21 +10025,21 @@
           <a:gradFill rotWithShape="1">
             <a:gsLst>
               <a:gs pos="0">
-                <a:schemeClr val="accent3">
+                <a:schemeClr val="accent1">
                   <a:satMod val="103000"/>
                   <a:lumMod val="102000"/>
                   <a:tint val="94000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="50000">
-                <a:schemeClr val="accent3">
+                <a:schemeClr val="accent1">
                   <a:satMod val="110000"/>
                   <a:lumMod val="100000"/>
                   <a:shade val="100000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="100000">
-                <a:schemeClr val="accent3">
+                <a:schemeClr val="accent1">
                   <a:lumMod val="99000"/>
                   <a:satMod val="120000"/>
                   <a:shade val="78000"/>
@@ -9730,13 +10229,11 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="lt1">
                         <a:lumMod val="85000"/>
@@ -9861,7 +10358,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="lt1">
                   <a:lumMod val="85000"/>
@@ -9918,7 +10415,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="600"/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -23019,6 +23516,7 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>409</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2800" b="1">
@@ -23419,6 +23917,7 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>407</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2800" b="1">
@@ -23562,8 +24061,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7365867" y="1149531"/>
-          <a:ext cx="7082895" cy="5800379"/>
+          <a:off x="7429732" y="1137920"/>
+          <a:ext cx="7146755" cy="5742322"/>
           <a:chOff x="11665528" y="4572000"/>
           <a:chExt cx="7126437" cy="5539122"/>
         </a:xfrm>
@@ -23741,6 +24240,7 @@
                 <a:ea typeface="Calibri"/>
                 <a:cs typeface="Calibri"/>
               </a:rPr>
+              <a:pPr algn="ctr"/>
               <a:t> $6,542,800 </a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="4400" b="1">
@@ -24591,8 +25091,8 @@
       <xdr:row>36</xdr:row>
       <xdr:rowOff>12835</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="1034" name="Department">
@@ -24615,7 +25115,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -24669,8 +25169,8 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>102670</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="1035" name="Designation">
@@ -24693,7 +25193,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -24747,8 +25247,8 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>154005</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="1036" name="Employee Category">
@@ -24771,7 +25271,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -24825,8 +25325,8 @@
       <xdr:row>27</xdr:row>
       <xdr:rowOff>89835</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="1037" name="Employee Type">
@@ -24849,7 +25349,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -24903,8 +25403,8 @@
       <xdr:row>35</xdr:row>
       <xdr:rowOff>115502</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="1038" name="Gender">
@@ -24927,7 +25427,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -24981,8 +25481,8 @@
       <xdr:row>27</xdr:row>
       <xdr:rowOff>166837</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="1039" name="Marital Status">
@@ -25005,7 +25505,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -25059,8 +25559,8 @@
       <xdr:row>70</xdr:row>
       <xdr:rowOff>102669</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="1040" name="Blood Group">
@@ -25083,7 +25583,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -25137,8 +25637,8 @@
       <xdr:row>35</xdr:row>
       <xdr:rowOff>115504</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="1041" name="Distance">
@@ -25161,7 +25661,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -25215,8 +25715,8 @@
       <xdr:row>35</xdr:row>
       <xdr:rowOff>166838</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="1042" name="Working status">
@@ -25239,7 +25739,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -25293,8 +25793,8 @@
       <xdr:row>60</xdr:row>
       <xdr:rowOff>51334</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="1043" name="Months (Date of Join)">
@@ -25317,7 +25817,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -25371,8 +25871,8 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>107036</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="1044" name="Quarters (Date of Join)">
@@ -25395,7 +25895,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -25449,8 +25949,8 @@
       <xdr:row>70</xdr:row>
       <xdr:rowOff>89834</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="1045" name="Years (Date of Join)">
@@ -25473,7 +25973,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -33115,278 +33615,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05F5957A-39FB-4F7D-BB15-035ECB9BD429}" name="PivotTable18" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="M28:N38" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="6"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="66">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="10">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="10">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total Employees" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{627827D4-CCE5-4D84-89CC-598C0608CB44}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{627827D4-CCE5-4D84-89CC-598C0608CB44}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="18">
     <pivotField dataField="1" showAll="0"/>
@@ -33613,8 +33842,3118 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ECF94918-46D4-41CA-A6CB-F7C98FDE0AB6}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Working Status">
+  <location ref="G3:H7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="66">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="13"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Active Employees" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="8" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4DE77CAB-0176-4550-8CA8-ED56551B90E9}" name="PivotTable9" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17" rowHeaderCaption="Designation">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EA4750D-7DCE-4AFB-9715-99348298E0FF}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Employee Type">
+  <location ref="D17:E20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="66">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Salary" fld="14" baseField="0" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="425">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{81C65711-0042-44DB-A9FE-09681C357C08}" name="PivotTable16" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="G23:H29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="66">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="6">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="12"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Employees" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="8" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4833C5FC-B665-44C1-985D-EDDC09DC1DF7}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C3:C4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="18">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="66">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Basic Salary" fld="14" baseField="0" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="426">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F039BB6F-060E-4CFD-8631-315ED5972007}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E3:E4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="18">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="66">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average Salary" fld="14" subtotal="average" baseField="0" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="427">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9C75FAD9-110A-488E-B0F5-F4E03F6C77D8}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="G10:H18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="8">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="66">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Salary" fld="14" subtotal="average" baseField="2" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="428">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24D03D5C-6B60-46AF-9108-5E29808B1F82}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Gender" colHeaderCaption="Employee Type">
+  <location ref="S3:T10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="66">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="8"/>
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="429">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{854CFCFD-E936-4C0F-8E4F-DC8718A10276}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+  <location ref="D10:E14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="66">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Employees" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="8" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D66152B6-023D-4DE7-9324-466BEEC91A3F}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+  <location ref="D23:E43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="66">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="2"/>
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="20">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of ID" fld="0" subtotal="count" baseField="2" baseItem="0" numFmtId="10">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{E15A36E0-9728-4e99-A89B-3F7291B0FE68}">
+          <x14:dataField pivotShowAs="percentOfParentRow"/>
+        </ext>
+      </extLst>
+    </dataField>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="431">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="430">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="7">
+    <chartFormat chart="13" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEAD4EAA-A79A-4B5D-B8D1-5C1082AB93D1}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16" rowHeaderCaption="Months">
+  <location ref="M3:N15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="66">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="15">
+        <item sd="0" x="13"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="15"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Number of Joined Employees" fld="0" subtotal="count" baseField="15" baseItem="1"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="417">
+      <pivotArea dataOnly="0" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="416">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="15" count="11">
+            <x v="2"/>
+            <x v="3"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="12"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="415">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="414">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="5">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="15" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1C4CE0DC-0A8D-46E4-937F-88FCF9C21156}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="A23:B26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="66">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Employees" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4DE77CAB-0176-4550-8CA8-ED56551B90E9}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17" rowHeaderCaption="Designation">
   <location ref="A8:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField dataField="1" showAll="0"/>
@@ -33932,799 +37271,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ECF94918-46D4-41CA-A6CB-F7C98FDE0AB6}" name="PivotTable4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Working Status">
-  <location ref="G3:H7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="6"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="66">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="13"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Active Employees" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="4">
-    <chartFormat chart="8" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F039BB6F-060E-4CFD-8631-315ED5972007}" name="PivotTable3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E3:E4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="18">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="6"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="66">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average Salary" fld="14" subtotal="average" baseField="0" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="224">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24D03D5C-6B60-46AF-9108-5E29808B1F82}" name="PivotTable6" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Gender" colHeaderCaption="Employee Type">
-  <location ref="S3:T10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="6"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="66">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="8"/>
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="225">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEAD4EAA-A79A-4B5D-B8D1-5C1082AB93D1}" name="PivotTable8" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16" rowHeaderCaption="Months">
-  <location ref="M3:N15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F525D377-7671-4C7F-A2BD-2D1E9689A6E4}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23" rowHeaderCaption="Months">
+  <location ref="K17:L22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
@@ -34889,7 +37438,7 @@
       </items>
     </pivotField>
     <pivotField numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
+    <pivotField showAll="0" sortType="descending">
       <items count="15">
         <item sd="0" x="13"/>
         <item sd="0" x="0"/>
@@ -34908,7 +37457,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="7">
         <item sd="0" x="0"/>
         <item sd="0" x="1"/>
@@ -34930,9 +37479,12 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="15"/>
+    <field x="16"/>
   </rowFields>
-  <rowItems count="12">
+  <rowItems count="5">
+    <i>
+      <x v="1"/>
+    </i>
     <i>
       <x v="2"/>
     </i>
@@ -34940,31 +37492,7 @@
       <x v="3"/>
     </i>
     <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
+      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -34976,37 +37504,18 @@
   <dataFields count="1">
     <dataField name="Number of Joined Employees" fld="0" subtotal="count" baseField="15" baseItem="1"/>
   </dataFields>
-  <formats count="4">
-    <format dxfId="229">
+  <formats count="3">
+    <format dxfId="420">
       <pivotArea dataOnly="0" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="228">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="15" count="11">
-            <x v="2"/>
-            <x v="3"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="12"/>
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="227">
+    <format dxfId="419">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="226">
+    <format dxfId="418">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="5">
+  <chartFormats count="7">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -35043,7 +37552,25 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="9" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
     <chartFormat chart="15" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="22" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -35065,8 +37592,279 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B105F544-AC66-4554-ABBB-10B138D9BBDF}" name="PivotTable5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Department">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05F5957A-39FB-4F7D-BB15-035ECB9BD429}" name="PivotTable18" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="M28:N38" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="66">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="10">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Employees" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B105F544-AC66-4554-ABBB-10B138D9BBDF}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Department">
   <location ref="J3:K11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField dataField="1" showAll="0"/>
@@ -35348,569 +38146,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8022FD-BBC3-4A32-96F3-E9CF2749AD18}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18" rowHeaderCaption="Designation">
-  <location ref="P3:Q14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="11">
-        <item x="6"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="66">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Salary" fld="14" subtotal="average" baseField="3" baseItem="5" numFmtId="166"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="233">
-      <pivotArea dataOnly="0" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="232">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="231">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="230">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="14" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4833C5FC-B665-44C1-985D-EDDC09DC1DF7}" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C3:C4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="18">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="6"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="66">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total Basic Salary" fld="14" baseField="0" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="234">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0431BA02-DE35-4B34-A153-AFF7437645CD}" name="PivotTable17" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0431BA02-DE35-4B34-A153-AFF7437645CD}" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="J28:K31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField dataField="1" showAll="0"/>
@@ -36183,1251 +38420,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{81C65711-0042-44DB-A9FE-09681C357C08}" name="PivotTable16" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="G23:H29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="6"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="66">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="6">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="12"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total Employees" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="8" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D66152B6-023D-4DE7-9324-466BEEC91A3F}" name="PivotTable15" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
-  <location ref="D23:E43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="6"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="66">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="2"/>
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="20">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of ID" fld="0" subtotal="count" baseField="2" baseItem="0" numFmtId="10">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{E15A36E0-9728-4e99-A89B-3F7291B0FE68}">
-          <x14:dataField pivotShowAs="percentOfParentRow"/>
-        </ext>
-      </extLst>
-    </dataField>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="218">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="217">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="7">
-    <chartFormat chart="13" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1C4CE0DC-0A8D-46E4-937F-88FCF9C21156}" name="PivotTable14" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="A23:B26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="6"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="66">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total Employees" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F525D377-7671-4C7F-A2BD-2D1E9689A6E4}" name="PivotTable13" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23" rowHeaderCaption="Months">
-  <location ref="K17:L22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="6"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="66">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0" sortType="descending">
-      <items count="15">
-        <item sd="0" x="13"/>
-        <item sd="0" x="0"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="16"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Number of Joined Employees" fld="0" subtotal="count" baseField="15" baseItem="1"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="219">
-      <pivotArea dataOnly="0" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="220">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="221">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="7">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="15" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="22" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EA4750D-7DCE-4AFB-9715-99348298E0FF}" name="PivotTable12" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Employee Type">
-  <location ref="D17:E20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8022FD-BBC3-4A32-96F3-E9CF2749AD18}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18" rowHeaderCaption="Designation">
+  <location ref="P3:Q14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -37443,7 +38438,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
       <items count="11">
         <item x="6"/>
         <item x="5"/>
@@ -37457,246 +38452,6 @@
         <item x="9"/>
         <item t="default"/>
       </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="66">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Salary" fld="14" baseField="0" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="222">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9C75FAD9-110A-488E-B0F5-F4E03F6C77D8}" name="PivotTable11" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="G10:H18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="8">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
       <autoSortScope>
         <pivotArea dataOnly="0" outline="0" fieldPosition="0">
           <references count="1">
@@ -37706,21 +38461,6 @@
           </references>
         </pivotArea>
       </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="6"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
     </pivotField>
     <pivotField showAll="0">
       <items count="4">
@@ -37897,20 +38637,23 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="2"/>
+    <field x="3"/>
   </rowFields>
-  <rowItems count="8">
+  <rowItems count="11">
     <i>
-      <x v="2"/>
+      <x v="3"/>
     </i>
     <i>
-      <x v="4"/>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="7"/>
     </i>
     <i>
       <x v="6"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="4"/>
     </i>
     <i>
       <x v="1"/>
@@ -37921,263 +38664,11 @@
     <i>
       <x v="5"/>
     </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Salary" fld="14" subtotal="average" baseField="2" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="223">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{854CFCFD-E936-4C0F-8E4F-DC8718A10276}" name="PivotTable10" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
-  <location ref="D10:E14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="6"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="66">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="4">
     <i>
-      <x/>
+      <x v="2"/>
     </i>
     <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
+      <x v="9"/>
     </i>
     <i t="grand">
       <x/>
@@ -38187,10 +38678,28 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Total Employees" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Average of Salary" fld="14" subtotal="average" baseField="3" baseItem="5" numFmtId="166"/>
   </dataFields>
+  <formats count="4">
+    <format dxfId="424">
+      <pivotArea dataOnly="0" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="423">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="422">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="421">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <chartFormats count="4">
-    <chartFormat chart="8" format="5" series="1">
+    <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -38199,38 +38708,29 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="8" format="6">
+    <chartFormat chart="2" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
+        <references count="1">
           <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="8" format="7">
+    <chartFormat chart="3" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
+        <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="8" format="8">
+    <chartFormat chart="14" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
+        <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
@@ -38705,7 +39205,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F301BFE2-11AB-419F-817D-0EED58731D71}" name="Table1" displayName="Table1" ref="A1:O410" totalsRowShown="0" headerRowDxfId="251" dataDxfId="250">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F301BFE2-11AB-419F-817D-0EED58731D71}" name="Table1" displayName="Table1" ref="A1:O410" totalsRowShown="0" headerRowDxfId="448" dataDxfId="447">
   <autoFilter ref="A1:O410" xr:uid="{F301BFE2-11AB-419F-817D-0EED58731D71}">
     <filterColumn colId="13">
       <filters>
@@ -38714,21 +39214,21 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{B9E743D1-CA6C-4CE3-B89C-68668F71CE4D}" name="ID" dataDxfId="249"/>
-    <tableColumn id="2" xr3:uid="{32FDCF9B-36DF-44DA-B44B-8AC2AB38682A}" name="Name" dataDxfId="248"/>
-    <tableColumn id="3" xr3:uid="{15E8095B-165B-452C-969B-762C8C7E691A}" name="Department" dataDxfId="247"/>
-    <tableColumn id="4" xr3:uid="{E9E95B7D-1FD7-406B-BF56-5A3FF93AA9F7}" name="Designation" dataDxfId="246"/>
-    <tableColumn id="5" xr3:uid="{B9CC7318-7882-4771-8C29-FE14751B0611}" name="Employee Category" dataDxfId="245"/>
-    <tableColumn id="6" xr3:uid="{78FE3916-49A3-41FD-B8EA-1A3173DB1931}" name="Employee Type" dataDxfId="244"/>
-    <tableColumn id="7" xr3:uid="{D0877FE1-4B2C-47D3-88D0-3AD040529BB0}" name="Date of confirmation" dataDxfId="243"/>
-    <tableColumn id="8" xr3:uid="{617EE741-636E-4FAF-88CC-F8E0DFE34AF7}" name="Date of Join" dataDxfId="242"/>
-    <tableColumn id="9" xr3:uid="{5A4AEB79-D2A6-4B8D-90A7-069F9E9F6226}" name="Gender" dataDxfId="241"/>
-    <tableColumn id="10" xr3:uid="{076D2466-34A7-4BD2-BE17-D4929EB07732}" name="Marital Status" dataDxfId="240"/>
-    <tableColumn id="11" xr3:uid="{F129C004-13E1-4E05-BFF2-1EF3E839CAB6}" name="Blood Group" dataDxfId="239"/>
-    <tableColumn id="12" xr3:uid="{0E9CD14C-2B9B-4DBF-8BD1-62F0945513CB}" name="Present Address" dataDxfId="238"/>
-    <tableColumn id="13" xr3:uid="{C825F419-785A-48EC-AD7D-CC3218E7AFCC}" name="Distance" dataDxfId="237"/>
-    <tableColumn id="14" xr3:uid="{13E71FFC-2FD5-4B68-A2B6-5BE6B1A02713}" name="Working status" dataDxfId="236"/>
-    <tableColumn id="15" xr3:uid="{21B4145A-DF43-46E7-9484-E2A779B8B230}" name="Salary" dataDxfId="235"/>
+    <tableColumn id="1" xr3:uid="{B9E743D1-CA6C-4CE3-B89C-68668F71CE4D}" name="ID" dataDxfId="446"/>
+    <tableColumn id="2" xr3:uid="{32FDCF9B-36DF-44DA-B44B-8AC2AB38682A}" name="Name" dataDxfId="445"/>
+    <tableColumn id="3" xr3:uid="{15E8095B-165B-452C-969B-762C8C7E691A}" name="Department" dataDxfId="444"/>
+    <tableColumn id="4" xr3:uid="{E9E95B7D-1FD7-406B-BF56-5A3FF93AA9F7}" name="Designation" dataDxfId="443"/>
+    <tableColumn id="5" xr3:uid="{B9CC7318-7882-4771-8C29-FE14751B0611}" name="Employee Category" dataDxfId="442"/>
+    <tableColumn id="6" xr3:uid="{78FE3916-49A3-41FD-B8EA-1A3173DB1931}" name="Employee Type" dataDxfId="441"/>
+    <tableColumn id="7" xr3:uid="{D0877FE1-4B2C-47D3-88D0-3AD040529BB0}" name="Date of confirmation" dataDxfId="440"/>
+    <tableColumn id="8" xr3:uid="{617EE741-636E-4FAF-88CC-F8E0DFE34AF7}" name="Date of Join" dataDxfId="439"/>
+    <tableColumn id="9" xr3:uid="{5A4AEB79-D2A6-4B8D-90A7-069F9E9F6226}" name="Gender" dataDxfId="438"/>
+    <tableColumn id="10" xr3:uid="{076D2466-34A7-4BD2-BE17-D4929EB07732}" name="Marital Status" dataDxfId="437"/>
+    <tableColumn id="11" xr3:uid="{F129C004-13E1-4E05-BFF2-1EF3E839CAB6}" name="Blood Group" dataDxfId="436"/>
+    <tableColumn id="12" xr3:uid="{0E9CD14C-2B9B-4DBF-8BD1-62F0945513CB}" name="Present Address" dataDxfId="435"/>
+    <tableColumn id="13" xr3:uid="{C825F419-785A-48EC-AD7D-CC3218E7AFCC}" name="Distance" dataDxfId="434"/>
+    <tableColumn id="14" xr3:uid="{13E71FFC-2FD5-4B68-A2B6-5BE6B1A02713}" name="Working status" dataDxfId="433"/>
+    <tableColumn id="15" xr3:uid="{21B4145A-DF43-46E7-9484-E2A779B8B230}" name="Salary" dataDxfId="432"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -58836,8 +59336,8 @@
     <col min="1" max="1" width="15.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.69921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.19921875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.09765625" bestFit="1" customWidth="1"/>
